--- a/data/raw/sw_industry_returns.xlsx
+++ b/data/raw/sw_industry_returns.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,21 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1303"/>
+  <dimension ref="A1:C1334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>行业</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>季度</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>涨跌幅</t>
         </is>
@@ -19973,6 +19961,471 @@
       </c>
       <c r="C1303" t="n">
         <v>-17.3161</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>15.104</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>基础化工</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>-13.5585</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>-1.3417</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>-10.464</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>-32.6465</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>-4.3128</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>家用电器</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>-0.2849</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>4.3358</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>纺织服饰</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>0.2627</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>轻工制造</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>-1.0406</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>10.1153</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>-0.7245</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>6.4401</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>9.357799999999999</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>商贸零售</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>2.7483</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>社会服务</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>0.0256</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>14.5576</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>非银金融</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>-3.3446</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>-4.3096</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>建筑材料</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>-26.0964</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>建筑装饰</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>-6.1639</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>-23.7314</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>-21.1077</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>国防军工</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>-12.5861</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>-8.131</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>-0.2132</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>-28.7191</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>19.2866</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>石油石化</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>15.3218</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>环保</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>-6.3862</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>美容护理</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>6.0708</v>
       </c>
     </row>
   </sheetData>
